--- a/Jira_Stories.xlsx
+++ b/Jira_Stories.xlsx
@@ -124,7 +124,681 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="75" customHeight="1">
+      <c r="A2" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Epic</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Build a secure cloud-native delivery platform</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Deliver an automated software supply chain that builds, assesses, remediates, deploys, scales, monitors, and protects containerized workloads.
+Definition of done:
+* The end-to-end path from source commit to EKS deployment is automated.
+* Vulnerable artifacts are blocked and secure artifacts are published.
+* Deployments are reconciled through GitOps.
+* Autoscaling, monitoring, dashboards, and runtime controls are operational.
+* Operating procedures and evidence for each control are documented.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">secure-platform</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Secure Cloud-Native Delivery Platform</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">SECPLAT</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Platform Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="75" customHeight="1">
+      <c r="A3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Trigger Jenkins CI from GitHub commits</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">As a developer, I want commits to trigger the Jenkins pipeline so that every change is validated consistently.
+Acceptance criteria:
+* Commits to configured branches trigger the correct pipeline.
+* The pipeline checks out the exact triggering revision.
+* Trigger and checkout failures are visible to developers.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">secure-platform</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Secure Cloud-Native Delivery Platform</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SECPLAT</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Platform Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="75" customHeight="1">
+      <c r="A4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Build an immutable container image</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">As a platform engineer, I want the pipeline to build a versioned container image so that releases are reproducible and traceable.
+Acceptance criteria:
+* The image build runs only after source checkout succeeds.
+* Every image is tagged with an immutable revision identifier.
+* Build failures stop all downstream stages.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">secure-platform</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Secure Cloud-Native Delivery Platform</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SECPLAT</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Platform Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="75" customHeight="1">
+      <c r="A5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Generate a software bill of materials</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">As a security engineer, I want an SBOM generated for every image so that included software components are auditable.
+Acceptance criteria:
+* Syft generates an SBOM for each built image.
+* The SBOM is stored as a pipeline artifact and linked to the image revision.
+* Failure to generate the SBOM blocks promotion.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">secure-platform</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Secure Cloud-Native Delivery Platform</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SECPLAT</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="75" customHeight="1">
+      <c r="A6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Scan images for known vulnerabilities</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">As a security engineer, I want each image scanned for CVEs so that vulnerable artifacts cannot be promoted.
+Acceptance criteria:
+* Grype or Trivy scans the built image and its packages.
+* Configurable severity thresholds determine pass or fail.
+* Scan findings are retained and visible from the pipeline.
+* Images above the threshold do not reach the registry.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">secure-platform</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Secure Cloud-Native Delivery Platform</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SECPLAT</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="75" customHeight="1">
+      <c r="A7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Analyze vulnerability findings with AI</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">As a developer, I want vulnerability findings enriched with remediation guidance so that issues can be resolved efficiently.
+Acceptance criteria:
+* Failed scan findings are sent to the analysis engine without credentials or secrets.
+* Recommendations identify the affected component, safe target version, and rationale.
+* Recommendations link back to the originating image and scan.
+* Uncertain recommendations are clearly marked for manual review.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">secure-platform</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Secure Cloud-Native Delivery Platform</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SECPLAT</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="75" customHeight="1">
+      <c r="A8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Revalidate remediated builds</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">As a security engineer, I want remediated changes to repeat the build and security checks so that only verified fixes are promoted.
+Acceptance criteria:
+* A remediation starts a new pipeline execution.
+* The image, SBOM, and CVE scan are regenerated.
+* Promotion occurs only when the configured security gate passes.
+* Retry limits prevent an uncontrolled remediation loop.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">secure-platform</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Secure Cloud-Native Delivery Platform</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SECPLAT</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="75" customHeight="1">
+      <c r="A9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Publish approved images to the registry</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">As a release engineer, I want approved images published to a registry so that deployment uses trusted artifacts.
+Acceptance criteria:
+* Only images that pass required pipeline gates are pushed.
+* Registry authentication uses managed credentials.
+* Published image digests and SBOM references are recorded.
+* Mutable tag overwrite is prevented for release images.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">secure-platform</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Secure Cloud-Native Delivery Platform</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SECPLAT</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Platform Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="75" customHeight="1">
+      <c r="A10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Deploy approved images through GitOps</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">As a platform engineer, I want approved image changes reconciled through GitOps so that cluster state is declarative and auditable.
+Acceptance criteria:
+* Deployment manifests reference an approved immutable image digest.
+* Changes are reviewed and committed to the GitOps source of truth.
+* The GitOps controller reconciles the change to EKS.
+* Failed reconciliation reports actionable status and supports rollback.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">secure-platform</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Secure Cloud-Native Delivery Platform</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SECPLAT</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Platform Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="75" customHeight="1">
+      <c r="A11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Provision EKS capacity with Karpenter</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">As a platform engineer, I want Karpenter to provision cluster nodes dynamically so that workloads receive capacity without static overprovisioning.
+Acceptance criteria:
+* Pending eligible workloads trigger node provisioning.
+* Node selection follows configured workload, security, and cost constraints.
+* Unused capacity is consolidated without disrupting protected workloads.
+* Provisioning and consolidation events are observable.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">secure-platform</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Secure Cloud-Native Delivery Platform</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SECPLAT</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Platform Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="75" customHeight="1">
+      <c r="A12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Collect platform and workload metrics</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">As an SRE, I want Prometheus to collect platform and workload metrics so that service health and capacity can be measured.
+Acceptance criteria:
+* Prometheus discovers and scrapes the agreed EKS targets.
+* Collection failures and storage pressure generate alerts.
+* Metric retention and access controls meet platform requirements.
+* Karpenter and workload health metrics are available for querying.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">secure-platform</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Secure Cloud-Native Delivery Platform</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SECPLAT</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Observability</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="75" customHeight="1">
+      <c r="A13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Provide operational Grafana dashboards</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">As an SRE, I want Grafana dashboards for delivery and runtime health so that teams can identify issues quickly.
+Acceptance criteria:
+* Dashboards show deployment, cluster, node, and workload health.
+* Dashboard panels use the Prometheus data source and document their queries.
+* Access follows least privilege.
+* Dashboard definitions are version controlled.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">secure-platform</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Secure Cloud-Native Delivery Platform</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SECPLAT</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Observability</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="75" customHeight="1">
+      <c r="A14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Story</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Enforce runtime security policies</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">As a security engineer, I want runtime policies enforced in EKS so that deployed workloads operate within approved boundaries.
+Acceptance criteria:
+* Policies cover privileged execution, image provenance, and other agreed controls.
+* Enforcement mode and exceptions are documented and auditable.
+* Violations generate actionable alerts.
+* Policy changes are tested before production enforcement.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">secure-platform</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Secure Cloud-Native Delivery Platform</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SECPLAT</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Security</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:I14"/>
 </worksheet>
 </file>